--- a/pre-week-2/homework1.xlsx
+++ b/pre-week-2/homework1.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thaniastaana\DataAnalytics\pre-week-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83968AA8-153A-4E7C-9A33-DB8A1AC277D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CF5CD29-90B7-419E-944F-D6CAB534DE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{B11F44AF-8627-44EA-A3F5-65B3AC6D0F03}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{B11F44AF-8627-44EA-A3F5-65B3AC6D0F03}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Store_Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Store_Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,6 +37,108 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+  <si>
+    <t>Store</t>
+  </si>
+  <si>
+    <t>Monthly
+ Sales</t>
+  </si>
+  <si>
+    <t>Store A</t>
+  </si>
+  <si>
+    <t>Store B</t>
+  </si>
+  <si>
+    <t>Store C</t>
+  </si>
+  <si>
+    <t>Store D</t>
+  </si>
+  <si>
+    <t>Store E</t>
+  </si>
+  <si>
+    <t>Store F</t>
+  </si>
+  <si>
+    <t>Store G</t>
+  </si>
+  <si>
+    <t>Store H</t>
+  </si>
+  <si>
+    <t>Store I</t>
+  </si>
+  <si>
+    <t>Store J</t>
+  </si>
+  <si>
+    <t>Store K</t>
+  </si>
+  <si>
+    <t>Store L</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t>Median</t>
+  </si>
+  <si>
+    <t>Mode</t>
+  </si>
+  <si>
+    <t>Range</t>
+  </si>
+  <si>
+    <t>Standard 
+Deviation</t>
+  </si>
+  <si>
+    <t>Standard
+Deviation (Without H)</t>
+  </si>
+  <si>
+    <t>The overall avergae is almost 50, so I think that is a good number</t>
+  </si>
+  <si>
+    <t>without the H anamoly, the performance was primarily tightly grouped</t>
+  </si>
+  <si>
+    <t>H can skew the results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I would add what the numbers represent </t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -69,8 +172,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,9 +511,186 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C63582D-5B04-469A-BA89-C97AC79EC976}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>51</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2">
+        <f xml:space="preserve"> AVERAGE(B2:B13)</f>
+        <v>49.416666666666664</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>44</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3">
+        <f>MEDIAN(B2:B13)</f>
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>49</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4">
+        <f>_xlfn.MODE.SNGL(B2:B13)</f>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" cm="1">
+        <f t="array" ref="E5">MAX(B2:B13-MIN(B2:B13))</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>47</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7">
+        <f>_xlfn.STDEV.S(B2:B13)</f>
+        <v>7.6331613054586773</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>45</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8">
+        <f>_xlfn.STDEV.S(B2:B8,B10:B13)</f>
+        <v>2.9076701075853588</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0263A048-A127-4427-AAA7-D574F6CA3606}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/pre-week-2/homework1.xlsx
+++ b/pre-week-2/homework1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thaniastaana\DataAnalytics\pre-week-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CF5CD29-90B7-419E-944F-D6CAB534DE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{19D29CB1-9196-41A2-9F3A-67D2A302BDA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{B11F44AF-8627-44EA-A3F5-65B3AC6D0F03}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{8EFF519F-EA2C-4242-A2D3-03B6B0C94DB2}"/>
   </bookViews>
   <sheets>
     <sheet name="Store_Data" sheetId="1" r:id="rId1"/>
@@ -95,7 +95,7 @@
     <t>Store H</t>
   </si>
   <si>
-    <t>Store I</t>
+    <t xml:space="preserve">Store I </t>
   </si>
   <si>
     <t>Store J</t>
@@ -119,24 +119,24 @@
     <t>Range</t>
   </si>
   <si>
-    <t>Standard 
-Deviation</t>
-  </si>
-  <si>
     <t>Standard
-Deviation (Without H)</t>
-  </si>
-  <si>
-    <t>The overall avergae is almost 50, so I think that is a good number</t>
-  </si>
-  <si>
-    <t>without the H anamoly, the performance was primarily tightly grouped</t>
-  </si>
-  <si>
-    <t>H can skew the results</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I would add what the numbers represent </t>
+ Deviation</t>
+  </si>
+  <si>
+    <t>Standard
+ Deviation (w/o H)</t>
+  </si>
+  <si>
+    <t>the overall performance is unknown beause we do not know what the data representsm, but the avg wa 50</t>
+  </si>
+  <si>
+    <t>tightly grouped, except an anomoly for store h</t>
+  </si>
+  <si>
+    <t>store h can skew the data</t>
+  </si>
+  <si>
+    <t>I would want info on what the data is representing and if it is sales, why store h had a higher number</t>
   </si>
 </sst>
 </file>
@@ -510,7 +510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C63582D-5B04-469A-BA89-C97AC79EC976}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D9EC82-B1F4-4C35-9CC1-50D24DE88259}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -533,7 +533,7 @@
         <v>14</v>
       </c>
       <c r="E2">
-        <f xml:space="preserve"> AVERAGE(B2:B13)</f>
+        <f>AVERAGE(B2:B13)</f>
         <v>49.416666666666664</v>
       </c>
     </row>
@@ -605,7 +605,7 @@
         <v>7.6331613054586773</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -666,7 +666,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0263A048-A127-4427-AAA7-D574F6CA3606}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C9C466B-4ED4-44AE-A63F-58AB8EA43322}">
   <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -693,4 +693,213 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100375F79C47DE8FF4FAF9EC5CCBFE2D46B" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8cf19172f4e0f3d30d68e0e61894b8e8">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="9df1e763-6145-4204-8e4d-63e05725baf0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b8772aff602974b3a0940237a25fcaa9" ns3:_="">
+    <xsd:import namespace="9df1e763-6145-4204-8e4d-63e05725baf0"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:_activity" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9df1e763-6145-4204-8e4d-63e05725baf0" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceDateTaken" ma:index="8" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_activity" ma:index="12" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="9df1e763-6145-4204-8e4d-63e05725baf0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4E45F0F-E355-472C-9351-0FCD55FD01DB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9df1e763-6145-4204-8e4d-63e05725baf0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{163CDA61-6606-422C-9D6D-6A69C4875B9C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01B55FBC-D272-47F3-B56C-B478EFDD5B83}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="9df1e763-6145-4204-8e4d-63e05725baf0"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>